--- a/docs/Horas proyecto estadistica.xlsx
+++ b/docs/Horas proyecto estadistica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Trabajo_final\AppClientesEstadistica\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E156FEB-04B2-4E69-9D9C-709377E1867C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0751B9E8-D6F6-4AE6-9881-43DEEDFE7B29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7980" activeTab="2" xr2:uid="{75DE17B3-81B2-44DB-AF0F-61090BDD4A63}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7980" xr2:uid="{75DE17B3-81B2-44DB-AF0F-61090BDD4A63}"/>
   </bookViews>
   <sheets>
     <sheet name="Funciones" sheetId="1" r:id="rId1"/>
@@ -194,47 +194,6 @@
 - Gestión rama producción</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Roberto =&gt; Login back y front
-Irantzu + Carlos + Roberto =&gt; Menu + Funcionalidades + Datos
-Sergio =&gt; Registro</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+ DevOps</t>
-    </r>
-  </si>
-  <si>
     <t>- Diseño funcionalidades menu
 - Metodo comprobación correo OK
 - Implementación login angular
@@ -264,10 +223,6 @@
 - Tablas</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Roberto y Carlos-&gt; Explicar tema lista con filtros a los muggles</t>
-  </si>
-  <si>
     <t>- Bogus
 - Implementar Bogus a front
 - Arreglar tostadora (ordenador)
@@ -295,24 +250,39 @@
 - Conectar clientes-back</t>
   </si>
   <si>
+    <t>Bogus no crea entidades</t>
+  </si>
+  <si>
     <t xml:space="preserve">- Hosteo en Azure
 - Variables de entorno
 - Solucionar merge NOK
 - Solucionar problema paquetes front
 - Rediseñar front estadistica
 - Mostrar graficas dinamicamente
-- 
+- Guia variables de entorno
+- Metodo de testeo back-front-BBDD
+- Aclarar tema BBDD resto equipos
 </t>
   </si>
   <si>
-    <t>Bogus no crea entidades</t>
+    <t xml:space="preserve">
+- Tener todo hosteado
+- Tener una versión entregable
+- Tener BBDD definitiva
+- Definir conexiones con resto equipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Roberto =&gt; Login back y front
+Irantzu + Carlos + Roberto =&gt; Menu + Funcionalidades + Datos
+Sergio =&gt; Registro + DevOps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,6 +343,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -771,6 +749,30 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -798,7 +800,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,30 +829,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1241,57 +1219,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="41" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="41" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="41" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="46"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="46"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="25"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1341,13 +1319,13 @@
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="17">
         <v>33</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1365,13 +1343,13 @@
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="18">
         <v>33</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -1389,13 +1367,13 @@
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="18">
         <v>33</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -1406,7 +1384,7 @@
       <c r="M7" s="10"/>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="108.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
@@ -1419,7 +1397,7 @@
         <v>33</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -1431,246 +1409,241 @@
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="39" t="s">
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="39" t="s">
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="39" t="s">
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="B10" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
     </row>
     <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B1:E3"/>
-    <mergeCell ref="L1:N3"/>
-    <mergeCell ref="I1:K3"/>
-    <mergeCell ref="F1:H3"/>
-    <mergeCell ref="L9:N9"/>
     <mergeCell ref="L10:N22"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E22"/>
@@ -1678,6 +1651,11 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K22"/>
+    <mergeCell ref="B1:E3"/>
+    <mergeCell ref="L1:N3"/>
+    <mergeCell ref="I1:K3"/>
+    <mergeCell ref="F1:H3"/>
+    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1735,7 +1713,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Horas proyecto estadistica.xlsx
+++ b/docs/Horas proyecto estadistica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Trabajo_final\AppClientesEstadistica\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0751B9E8-D6F6-4AE6-9881-43DEEDFE7B29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD816F67-EB90-4F0F-BED5-EC26B077A074}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7980" xr2:uid="{75DE17B3-81B2-44DB-AF0F-61090BDD4A63}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="41">
   <si>
     <t>Roberto</t>
   </si>
@@ -266,16 +266,45 @@
   </si>
   <si>
     <t xml:space="preserve">
-- Tener todo hosteado
-- Tener una versión entregable
-- Tener BBDD definitiva
-- Definir conexiones con resto equipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
 Roberto =&gt; Login back y front
 Irantzu + Carlos + Roberto =&gt; Menu + Funcionalidades + Datos
 Sergio =&gt; Registro + DevOps</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Tener todo hosteado</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Tener una versión entregable
+- Tener BBDD definitiva
+- Definir conexiones con resto equipo
+Sergio =&gt; Apartado display graficas estadistica</t>
+    </r>
+  </si>
+  <si>
+    <t>- Implementar 8 graficas máx
+- Normalizar tamaño graficas</t>
   </si>
 </sst>
 </file>
@@ -692,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -766,6 +795,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1218,7 +1271,7 @@
     <col min="14" max="14" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>14</v>
       </c>
@@ -1228,8 +1281,8 @@
       <c r="F1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
       <c r="I1" s="20" t="s">
         <v>16</v>
       </c>
@@ -1241,14 +1294,14 @@
       <c r="M1" s="21"/>
       <c r="N1" s="22"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="25"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="23"/>
       <c r="J2" s="24"/>
       <c r="K2" s="25"/>
@@ -1256,14 +1309,14 @@
       <c r="M2" s="24"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="23"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
       <c r="E3" s="25"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
       <c r="I3" s="23"/>
       <c r="J3" s="24"/>
       <c r="K3" s="25"/>
@@ -1327,7 +1380,9 @@
       <c r="F5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="16" t="s">
+        <v>40</v>
+      </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -1409,238 +1464,238 @@
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="26" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="26" t="s">
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="26" t="s">
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
     </row>
     <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/docs/Horas proyecto estadistica.xlsx
+++ b/docs/Horas proyecto estadistica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Trabajo_final\AppClientesEstadistica\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD816F67-EB90-4F0F-BED5-EC26B077A074}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A5D59E-E0B7-4BCE-8D47-892861F81A89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7980" xr2:uid="{75DE17B3-81B2-44DB-AF0F-61090BDD4A63}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>Roberto</t>
   </si>
@@ -269,6 +269,13 @@
 Roberto =&gt; Login back y front
 Irantzu + Carlos + Roberto =&gt; Menu + Funcionalidades + Datos
 Sergio =&gt; Registro + DevOps</t>
+  </si>
+  <si>
+    <t>- Implementar 8 graficas máx
+- Normalizar tamaño graficas</t>
+  </si>
+  <si>
+    <t>Asociacion entre tablas</t>
   </si>
   <si>
     <r>
@@ -298,13 +305,31 @@
       <t xml:space="preserve">
 - Tener una versión entregable
 - Tener BBDD definitiva
-- Definir conexiones con resto equipo
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Definir conexiones con resto equipo</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 Sergio =&gt; Apartado display graficas estadistica</t>
     </r>
-  </si>
-  <si>
-    <t>- Implementar 8 graficas máx
-- Normalizar tamaño graficas</t>
   </si>
 </sst>
 </file>
@@ -778,6 +803,69 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -819,69 +907,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1272,57 +1297,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="20" t="s">
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="20" t="s">
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="20" t="s">
+      <c r="J1" s="42"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="22"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="25"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="46"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="25"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="46"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1381,7 +1406,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
@@ -1464,241 +1489,246 @@
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="34" t="s">
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="34" t="s">
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="34" t="s">
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="54" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="48"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
     </row>
     <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B1:E3"/>
+    <mergeCell ref="L1:N3"/>
+    <mergeCell ref="I1:K3"/>
+    <mergeCell ref="F1:H3"/>
+    <mergeCell ref="L9:N9"/>
     <mergeCell ref="L10:N22"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E22"/>
@@ -1706,11 +1736,6 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K22"/>
-    <mergeCell ref="B1:E3"/>
-    <mergeCell ref="L1:N3"/>
-    <mergeCell ref="I1:K3"/>
-    <mergeCell ref="F1:H3"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1748,7 +1773,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC113B12-C74D-416E-884F-DBDB84D406B9}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1771,6 +1796,11 @@
         <v>36</v>
       </c>
     </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Horas proyecto estadistica.xlsx
+++ b/docs/Horas proyecto estadistica.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Trabajo_final\AppClientesEstadistica\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A5D59E-E0B7-4BCE-8D47-892861F81A89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EF0869-B20D-4409-A0A0-8E0ABBE61541}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7980" xr2:uid="{75DE17B3-81B2-44DB-AF0F-61090BDD4A63}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>Roberto</t>
   </si>
@@ -331,12 +331,15 @@
 Sergio =&gt; Apartado display graficas estadistica</t>
     </r>
   </si>
+  <si>
+    <t>Archivo Obsoleto</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,6 +408,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -456,7 +467,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -742,11 +753,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -803,6 +851,54 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -860,53 +956,14 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -929,16 +986,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2028825</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2028826</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247651</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -953,8 +1010,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="9363075" y="0"/>
-          <a:ext cx="1" cy="6000750"/>
+          <a:off x="11677650" y="85725"/>
+          <a:ext cx="1" cy="6153150"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1297,57 +1354,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="41" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="41" t="s">
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="41" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="46"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="46"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="25"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1409,7 +1466,9 @@
         <v>39</v>
       </c>
       <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="I5" s="57" t="s">
+        <v>42</v>
+      </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -1433,7 +1492,7 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="I6" s="55"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
@@ -1457,7 +1516,7 @@
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="I7" s="55"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -1481,7 +1540,7 @@
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
+      <c r="I8" s="56"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
@@ -1489,246 +1548,241 @@
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="39" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="39" t="s">
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="39" t="s">
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="38" t="s">
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
     </row>
     <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B1:E3"/>
-    <mergeCell ref="L1:N3"/>
-    <mergeCell ref="I1:K3"/>
-    <mergeCell ref="F1:H3"/>
-    <mergeCell ref="L9:N9"/>
+  <mergeCells count="13">
     <mergeCell ref="L10:N22"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E22"/>
@@ -1736,6 +1790,12 @@
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K22"/>
+    <mergeCell ref="B1:E3"/>
+    <mergeCell ref="L1:N3"/>
+    <mergeCell ref="I1:K3"/>
+    <mergeCell ref="F1:H3"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="I5:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
